--- a/outputs/step3_disease_logistic/ckd/ckd_logistic_coefficients.xlsx
+++ b/outputs/step3_disease_logistic/ckd/ckd_logistic_coefficients.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic4" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic4_aec_best" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic5_aec_best" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,10 +454,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7073</v>
+        <v>1.7015</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5142</v>
+        <v>5.482</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +467,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7216</v>
+        <v>0.7103</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0577</v>
+        <v>2.0346</v>
       </c>
     </row>
     <row r="4">
@@ -479,10 +480,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2264</v>
+        <v>-0.2259</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7974</v>
+        <v>0.7978</v>
       </c>
     </row>
     <row r="5">
@@ -492,10 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1381</v>
+        <v>0.1397</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1481</v>
+        <v>1.1499</v>
       </c>
     </row>
     <row r="6">
@@ -505,10 +506,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.651</v>
+        <v>-3.6294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.026</v>
+        <v>0.0265</v>
       </c>
     </row>
   </sheetData>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,10 +550,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.4306</v>
+        <v>1.4492</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1813</v>
+        <v>4.2595</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +563,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5668</v>
+        <v>0.5523</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7627</v>
+        <v>1.7373</v>
       </c>
     </row>
     <row r="4">
@@ -575,10 +576,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0893</v>
+        <v>-0.0327</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9146</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="5">
@@ -588,62 +589,288 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2147</v>
+        <v>-0.2419</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8067</v>
+        <v>0.7851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aec_best_aec_fpca_0</t>
+          <t>aec_best_aec_shape_all_0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3753</v>
+        <v>-0.4051</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4555</v>
+        <v>0.6669</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aec_best_aec_fpca_1</t>
+          <t>aec_best_aec_shape_all_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.496</v>
+        <v>0.1857</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6089</v>
+        <v>1.2041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aec_best_aec_fpca_2</t>
+          <t>aec_best_aec_shape_all_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0033</v>
+        <v>0.0089</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0033</v>
+        <v>1.0089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>aec_best_aec_shape_all_3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.6893</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.3197</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>intercept</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>-3.7198</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sex_M</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.7474</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.7397</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.8524</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0204</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.251</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7781</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>vat_sat_ratio</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.3748</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6874</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6783</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.2115</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_2</t>
+        </is>
+      </c>
       <c r="B9" t="n">
-        <v>-3.6668</v>
+        <v>-0.1837</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0256</v>
+        <v>0.8322000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.3509</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aec_best_aec_shape_all_5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.1031</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9021</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-3.8713</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0208</v>
       </c>
     </row>
   </sheetData>
